--- a/src/test/resources/Appmnt_admin.xlsx
+++ b/src/test/resources/Appmnt_admin.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="56">
   <si>
     <t>Client:</t>
   </si>
@@ -166,6 +166,21 @@
   </si>
   <si>
     <t>'Screenshots'!A404</t>
+  </si>
+  <si>
+    <t>'Screenshots'!A435</t>
+  </si>
+  <si>
+    <t>'Screenshots'!A466</t>
+  </si>
+  <si>
+    <t>'Screenshots'!A497</t>
+  </si>
+  <si>
+    <t>'Screenshots'!A528</t>
+  </si>
+  <si>
+    <t>'Screenshots'!A559</t>
   </si>
 </sst>
 </file>
@@ -173,7 +188,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="16">
+  <fonts count="21">
     <font>
       <sz val="11.0"/>
       <color indexed="8"/>
@@ -185,6 +200,36 @@
       <name val="Calibri"/>
       <sz val="11.0"/>
       <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <u val="single"/>
+      <color indexed="12"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <u val="single"/>
+      <color indexed="12"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <u val="single"/>
+      <color indexed="12"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <u val="single"/>
+      <color indexed="12"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <u val="single"/>
+      <color indexed="12"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -301,7 +346,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="true"/>
@@ -319,6 +364,11 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true"/>
   </cellXfs>
 </styleSheet>
 </file>
@@ -857,12 +907,202 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="twoCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>434</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>454998</xdr:colOff>
+      <xdr:row>459</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="15" name="Picture 1" descr="Picture"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="true"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId15"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="9525000" cy="4762500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="twoCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>465</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>454998</xdr:colOff>
+      <xdr:row>490</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="16" name="Picture 1" descr="Picture"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="true"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId16"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="9525000" cy="4762500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="twoCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>496</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>454998</xdr:colOff>
+      <xdr:row>521</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="17" name="Picture 1" descr="Picture"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="true"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId17"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="9525000" cy="4762500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="twoCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>527</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>454998</xdr:colOff>
+      <xdr:row>552</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="18" name="Picture 1" descr="Picture"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="true"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId18"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="9525000" cy="4762500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="twoCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>558</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>454998</xdr:colOff>
+      <xdr:row>583</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="19" name="Picture 1" descr="Picture"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="true"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId19"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="9525000" cy="4762500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1209,6 +1449,106 @@
       </c>
       <c r="F21" t="s" s="16">
         <v>50</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="B22" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C22" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="D22" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="E22" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="F22" t="s" s="17">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="B23" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="C23" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="D23" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="E23" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="F23" t="s" s="18">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="B24" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="C24" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="D24" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="E24" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="F24" t="s" s="19">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="B25" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C25" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="D25" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="E25" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="F25" t="s" s="20">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="B26" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="C26" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="D26" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="E26" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="F26" t="s" s="21">
+        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -1227,6 +1567,11 @@
     <hyperlink location="'Screenshots'!A342" ref="F19"/>
     <hyperlink location="'Screenshots'!A373" ref="F20"/>
     <hyperlink location="'Screenshots'!A404" ref="F21"/>
+    <hyperlink location="'Screenshots'!A435" ref="F22"/>
+    <hyperlink location="'Screenshots'!A466" ref="F23"/>
+    <hyperlink location="'Screenshots'!A497" ref="F24"/>
+    <hyperlink location="'Screenshots'!A528" ref="F25"/>
+    <hyperlink location="'Screenshots'!A559" ref="F26"/>
   </hyperlinks>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
@@ -1234,7 +1579,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A404"/>
+  <dimension ref="A1:A559"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1278,6 +1623,21 @@
     </row>
     <row r="404">
       <c r="A404" s="0"/>
+    </row>
+    <row r="435">
+      <c r="A435" s="0"/>
+    </row>
+    <row r="466">
+      <c r="A466" s="0"/>
+    </row>
+    <row r="497">
+      <c r="A497" s="0"/>
+    </row>
+    <row r="528">
+      <c r="A528" s="0"/>
+    </row>
+    <row r="559">
+      <c r="A559" s="0"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
